--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F5970B-9070-432A-B1E2-A0271AC7EEC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29EE199-A47E-49D8-9C73-24D21B2E6B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -599,8 +599,8 @@
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="4"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="5"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
       <c r="G4" s="5"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -614,7 +614,7 @@
         <v>7</v>
       </c>
       <c r="C5" s="11"/>
-      <c r="D5" s="5"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="5"/>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>

--- a/docs/gantt_diagram.xlsx
+++ b/docs/gantt_diagram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ML\Quiz\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29EE199-A47E-49D8-9C73-24D21B2E6B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69093E90-2BFC-44DC-97DF-F64C3852A6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B210EFAB-924B-4A60-8CEF-576CA82F8EBB}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Bejelentkezés</t>
   </si>
@@ -58,23 +58,29 @@
     <t>Adatbázis</t>
   </si>
   <si>
-    <t>Php</t>
-  </si>
-  <si>
     <t>Főoldal</t>
   </si>
   <si>
-    <t>Css</t>
-  </si>
-  <si>
     <t>Reszponzivitás</t>
+  </si>
+  <si>
+    <t>Dokumentáció</t>
+  </si>
+  <si>
+    <t>PPT</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>CSS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +126,13 @@
       <family val="2"/>
       <charset val="238"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -153,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -173,9 +186,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -184,6 +194,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -541,7 +558,9 @@
       <c r="K1" s="1">
         <v>46125</v>
       </c>
-      <c r="L1" s="1"/>
+      <c r="L1" s="1">
+        <v>46132</v>
+      </c>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -563,8 +582,8 @@
         <v>0</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
@@ -575,7 +594,7 @@
       <c r="M2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -585,7 +604,7 @@
       <c r="D3" s="4"/>
       <c r="E3" s="5"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="11"/>
+      <c r="G3" s="10"/>
       <c r="H3" s="4"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -597,7 +616,7 @@
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -611,32 +630,32 @@
     </row>
     <row r="5" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+        <v>11</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="11"/>
+        <v>7</v>
+      </c>
+      <c r="C6" s="10"/>
       <c r="D6" s="4"/>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="5"/>
-      <c r="J6" s="11"/>
+      <c r="J6" s="10"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
@@ -645,17 +664,17 @@
     </row>
     <row r="7" spans="1:26" ht="18" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="10"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="11"/>
+      <c r="K7" s="10"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -663,17 +682,17 @@
     </row>
     <row r="8" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
-      <c r="K8" s="13"/>
+      <c r="K8" s="12"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -682,17 +701,19 @@
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="9"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="9"/>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="4"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
+      <c r="L9" s="4"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
@@ -701,6 +722,12 @@
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
     </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="B10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="4"/>
+    </row>
     <row r="15" spans="1:26" ht="18" x14ac:dyDescent="0.2">
       <c r="J15" s="8"/>
     </row>
